--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korbinian.zacherl\Documents\UiPath\EWO_neu\uipath-rpa_ewo_performer\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korbinian.zacherl\Documents\UiPath\EWO_neu\uipath-rpa_ewo_prod\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93F604DB-3F35-4D2D-9770-3BF244862EFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C443E413-BE9A-4AA0-8927-5F46CD14CE0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -240,7 +240,7 @@
     <t>javaw</t>
   </si>
   <si>
-    <t>ProcessEWOQueue</t>
+    <t>ProcessEWOQueueProd</t>
   </si>
 </sst>
 </file>
@@ -292,7 +292,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -303,7 +303,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -619,12 +618,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z998"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="43.5546875" customWidth="1"/>
+    <col min="1" max="1" width="43.5703125" customWidth="1"/>
     <col min="2" max="2" width="43" customWidth="1"/>
-    <col min="3" max="3" width="81.44140625" customWidth="1"/>
-    <col min="4" max="26" width="8.6640625" customWidth="1"/>
+    <col min="3" max="3" width="81.42578125" customWidth="1"/>
+    <col min="4" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
@@ -665,14 +664,14 @@
       <c r="A2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" t="s">
         <v>71</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="43.2">
+    <row r="3" spans="1:26" ht="45">
       <c r="A3" s="2" t="s">
         <v>31</v>
       </c>
@@ -682,7 +681,7 @@
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="5" spans="1:26" ht="28.8">
+    <row r="5" spans="1:26" ht="30">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -1696,12 +1695,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Z998"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
     <col min="2" max="2" width="51" customWidth="1"/>
-    <col min="3" max="3" width="75.44140625" customWidth="1"/>
-    <col min="4" max="26" width="8.6640625" customWidth="1"/>
+    <col min="3" max="3" width="75.42578125" customWidth="1"/>
+    <col min="4" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
@@ -1738,7 +1737,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="28.8">
+    <row r="2" spans="1:26" ht="30">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -1749,7 +1748,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="28.8">
+    <row r="3" spans="1:26" ht="30">
       <c r="A3" s="4" t="s">
         <v>44</v>
       </c>
@@ -1760,7 +1759,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="43.2">
+    <row r="4" spans="1:26" ht="45">
       <c r="A4" s="4" t="s">
         <v>33</v>
       </c>
@@ -1771,7 +1770,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:26" s="4" customFormat="1" ht="14.4">
+    <row r="5" spans="1:26" s="4" customFormat="1">
       <c r="A5" s="4" t="s">
         <v>46</v>
       </c>
@@ -1807,7 +1806,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:26" s="4" customFormat="1" ht="14.4">
+    <row r="9" spans="1:26" s="4" customFormat="1">
       <c r="A9" s="4" t="s">
         <v>48</v>
       </c>
@@ -1818,8 +1817,8 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:26" s="4" customFormat="1" ht="14.4"/>
-    <row r="11" spans="1:26" s="4" customFormat="1" ht="14.4">
+    <row r="10" spans="1:26" s="4" customFormat="1"/>
+    <row r="11" spans="1:26" s="4" customFormat="1">
       <c r="A11" s="4" t="s">
         <v>49</v>
       </c>
@@ -1830,7 +1829,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:26" s="4" customFormat="1" ht="14.4">
+    <row r="12" spans="1:26" s="4" customFormat="1">
       <c r="A12" s="4" t="s">
         <v>50</v>
       </c>
@@ -1841,7 +1840,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:26" s="4" customFormat="1" ht="14.4">
+    <row r="13" spans="1:26" s="4" customFormat="1">
       <c r="A13" s="4" t="s">
         <v>51</v>
       </c>
@@ -1852,7 +1851,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="14" spans="1:26" s="4" customFormat="1" ht="14.4">
+    <row r="14" spans="1:26" s="4" customFormat="1">
       <c r="A14" s="4" t="s">
         <v>53</v>
       </c>
@@ -1863,7 +1862,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="1:26" s="4" customFormat="1" ht="14.4">
+    <row r="15" spans="1:26" s="4" customFormat="1">
       <c r="A15" s="4" t="s">
         <v>55</v>
       </c>
@@ -1977,7 +1976,7 @@
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
     </row>
-    <row r="27" spans="1:3" ht="28.8">
+    <row r="27" spans="1:3" ht="45">
       <c r="A27" s="4" t="s">
         <v>40</v>
       </c>
@@ -2967,11 +2966,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Z996"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="2" width="35.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="60.33203125" customWidth="1"/>
-    <col min="4" max="26" width="65.44140625" customWidth="1"/>
+    <col min="1" max="2" width="35.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="60.28515625" customWidth="1"/>
+    <col min="4" max="26" width="65.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korbinian.zacherl\Documents\UiPath\EWO_neu\uipath-rpa_ewo_prod\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C443E413-BE9A-4AA0-8927-5F46CD14CE0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A880BCC3-CDB1-42C6-AEAC-463D89E2BC73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12468" yWindow="13584" windowWidth="17280" windowHeight="8928" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -240,7 +240,7 @@
     <t>javaw</t>
   </si>
   <si>
-    <t>ProcessEWOQueueProd</t>
+    <t>ProcessEWOQueue</t>
   </si>
 </sst>
 </file>
